--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N133_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N133_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>52.44603405076882</v>
+        <v>8.522480533249935</v>
       </c>
       <c r="D2" t="n">
-        <v>15.57102478353403</v>
+        <v>2.53029152732428</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
